--- a/InputData/trans/BLP/BAU LCFS Perc.xlsx
+++ b/InputData/trans/BLP/BAU LCFS Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zefania\Career\EPS-IESR\BLP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/BLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5CB260-7E5D-4060-A111-B0A560D5B517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCED91C-2A24-954A-B56A-6432245B0806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,19 @@
     <sheet name="BLP" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -99,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -683,7 +696,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -694,11 +707,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="43" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="65">
@@ -831,9 +843,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -871,9 +883,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -906,26 +918,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -958,26 +953,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1152,18 +1130,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="56.77734375" customWidth="1"/>
+    <col min="2" max="2" width="56.83203125" customWidth="1"/>
     <col min="5" max="5" width="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1174,15 +1152,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>2015</v>
       </c>
@@ -1190,7 +1168,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>7</v>
       </c>
@@ -1198,7 +1176,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
@@ -1206,17 +1184,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="64" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1233,37 +1211,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9973483C-F24E-445D-B023-11424C9B6CAC}">
   <dimension ref="A2:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>0.2903</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <f>B2*B3</f>
         <v>8.7090000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1276,23 +1254,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE0380E-4BEB-480A-8337-62D4AD2B0F07}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1300,30 +1278,22 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>0.81</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <f>B4/B3*100</f>
         <v>29.032258064516132</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1335,111 +1305,171 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BA2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>2019</v>
       </c>
       <c r="C1">
         <v>2020</v>
       </c>
-      <c r="D1" s="8">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="E1" s="8">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="F1" s="8">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="G1" s="8">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="H1" s="8">
+      <c r="H1">
         <v>2025</v>
       </c>
-      <c r="I1" s="8">
+      <c r="I1">
         <v>2026</v>
       </c>
-      <c r="J1" s="8">
+      <c r="J1">
         <v>2027</v>
       </c>
-      <c r="K1" s="8">
+      <c r="K1">
         <v>2028</v>
       </c>
-      <c r="L1" s="8">
+      <c r="L1">
         <v>2029</v>
       </c>
-      <c r="M1" s="8">
+      <c r="M1">
         <v>2030</v>
       </c>
-      <c r="N1" s="8">
+      <c r="N1">
         <v>2031</v>
       </c>
-      <c r="O1" s="8">
+      <c r="O1">
         <v>2032</v>
       </c>
-      <c r="P1" s="8">
+      <c r="P1">
         <v>2033</v>
       </c>
-      <c r="Q1" s="8">
+      <c r="Q1">
         <v>2034</v>
       </c>
-      <c r="R1" s="8">
+      <c r="R1">
         <v>2035</v>
       </c>
-      <c r="S1" s="8">
+      <c r="S1">
         <v>2036</v>
       </c>
-      <c r="T1" s="8">
+      <c r="T1">
         <v>2037</v>
       </c>
-      <c r="U1" s="8">
+      <c r="U1">
         <v>2038</v>
       </c>
-      <c r="V1" s="8">
+      <c r="V1">
         <v>2039</v>
       </c>
-      <c r="W1" s="8">
+      <c r="W1">
         <v>2040</v>
       </c>
-      <c r="X1" s="8">
+      <c r="X1">
         <v>2041</v>
       </c>
-      <c r="Y1" s="8">
+      <c r="Y1">
         <v>2042</v>
       </c>
-      <c r="Z1" s="8">
+      <c r="Z1">
         <v>2043</v>
       </c>
-      <c r="AA1" s="8">
+      <c r="AA1">
         <v>2044</v>
       </c>
-      <c r="AB1" s="8">
+      <c r="AB1">
         <v>2045</v>
       </c>
-      <c r="AC1" s="8">
+      <c r="AC1">
         <v>2046</v>
       </c>
-      <c r="AD1" s="8">
+      <c r="AD1">
         <v>2047</v>
       </c>
-      <c r="AE1" s="8">
+      <c r="AE1">
         <v>2048</v>
       </c>
-      <c r="AF1" s="8">
+      <c r="AF1">
         <v>2049</v>
       </c>
-      <c r="AG1" s="8">
+      <c r="AG1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="AH1">
+        <v>2051</v>
+      </c>
+      <c r="AI1">
+        <v>2052</v>
+      </c>
+      <c r="AJ1">
+        <v>2053</v>
+      </c>
+      <c r="AK1">
+        <v>2054</v>
+      </c>
+      <c r="AL1">
+        <v>2055</v>
+      </c>
+      <c r="AM1">
+        <v>2056</v>
+      </c>
+      <c r="AN1">
+        <v>2057</v>
+      </c>
+      <c r="AO1">
+        <v>2058</v>
+      </c>
+      <c r="AP1">
+        <v>2059</v>
+      </c>
+      <c r="AQ1">
+        <v>2060</v>
+      </c>
+      <c r="AR1">
+        <v>2061</v>
+      </c>
+      <c r="AS1">
+        <v>2062</v>
+      </c>
+      <c r="AT1">
+        <v>2063</v>
+      </c>
+      <c r="AU1">
+        <v>2064</v>
+      </c>
+      <c r="AV1">
+        <v>2065</v>
+      </c>
+      <c r="AW1">
+        <v>2066</v>
+      </c>
+      <c r="AX1">
+        <v>2067</v>
+      </c>
+      <c r="AY1">
+        <v>2068</v>
+      </c>
+      <c r="AZ1">
+        <v>2069</v>
+      </c>
+      <c r="BA1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1571,9 +1601,86 @@
         <f>calculation!$B$4</f>
         <v>8.7090000000000001E-2</v>
       </c>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
+      <c r="AH2" s="6">
+        <f>AG2</f>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AI2" s="6">
+        <f t="shared" ref="AI2:BA2" si="0">AH2</f>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AJ2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AK2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AL2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AM2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AN2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AO2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AP2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AQ2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AR2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AS2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AT2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AU2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AV2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AW2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AX2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AY2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="AZ2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
+      <c r="BA2" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7090000000000001E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/trans/BLP/BAU LCFS Perc.xlsx
+++ b/InputData/trans/BLP/BAU LCFS Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/BLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCED91C-2A24-954A-B56A-6432245B0806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F8F9DE-F257-A444-9DD3-E12991D94367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1474,212 +1474,160 @@
         <v>5</v>
       </c>
       <c r="B2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="L2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="N2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="O2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="R2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="S2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="T2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="U2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="V2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="W2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="X2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="6">
-        <f>calculation!$B$4</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="6">
-        <f>AG2</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="6">
-        <f t="shared" ref="AI2:BA2" si="0">AH2</f>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AM2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AU2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AW2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AX2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AY2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AZ2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="BA2" s="6">
-        <f t="shared" si="0"/>
-        <v>8.7090000000000001E-2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
